--- a/Result/profitability/3531.xlsx
+++ b/Result/profitability/3531.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.43</v>
       </c>
       <c r="M2" t="n">
-        <v>0.135</v>
+        <v>0.22375</v>
       </c>
       <c r="N2" t="n">
-        <v>14.7225</v>
+        <v>16.84375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.29</v>
       </c>
       <c r="M3" t="n">
-        <v>0.28125</v>
+        <v>0.14625</v>
       </c>
       <c r="N3" t="n">
-        <v>17.155</v>
+        <v>17.18375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>0.245</v>
+        <v>0.175</v>
       </c>
       <c r="N4" t="n">
-        <v>17.7</v>
+        <v>17.27</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.22</v>
       </c>
       <c r="M5" t="n">
-        <v>0.22375</v>
+        <v>0.35875</v>
       </c>
       <c r="N5" t="n">
-        <v>16.8675</v>
+        <v>15.88</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3975</v>
+        <v>0.3275</v>
       </c>
       <c r="N6" t="n">
-        <v>15.97875</v>
+        <v>17.24625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,13 +1264,13 @@
         <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>0.39</v>
+        <v>0.27375</v>
       </c>
       <c r="N7" t="n">
-        <v>17.7875</v>
+        <v>16.7375</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.85</v>
       </c>
       <c r="M8" t="n">
-        <v>0.40125</v>
+        <v>0.33875</v>
       </c>
       <c r="N8" t="n">
-        <v>17.725</v>
+        <v>17.0225</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -1518,7 +1518,7 @@
         <v>0.52</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4249999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="N9" t="n">
         <v>17.84125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3531</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>258</v>
+      </c>
+      <c r="D75" t="n">
+        <v>221</v>
+      </c>
+      <c r="E75" t="n">
+        <v>37</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-17</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-6.54%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.06000000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.0925</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.515151515151515</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.620000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.281563126252505</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.864</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.899999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3552158273381295</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
